--- a/outputs/daily/hr_rankings_2026-10-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-08.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>38</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -910,12 +910,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>52.7</v>
       </c>
       <c r="Q3" t="n">
         <v>21.5</v>
@@ -1209,13 +1209,13 @@
         <v>38</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>41.2</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1300,72 +1300,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>91.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0711</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4717</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.1998</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>45.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.2472</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1451,24 +1451,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1518,22 +1518,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R4" t="n">
         <v>38</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>34.9</v>
+        <v>41.2</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -1546,24 +1546,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1608,112 +1608,112 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.2069</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1769,24 +1769,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -1799,17 +1799,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.4</v>
+        <v>47.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,26 +1832,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>38</v>
       </c>
       <c r="S5" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>66</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1864,24 +1864,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1916,22 +1916,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1941,97 +1941,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.63</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.0711</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4717</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1998</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2472</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>502054</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Tommy Pham</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.1</v>
+        <v>44.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -2163,13 +2163,13 @@
         <v>38</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>44.1</v>
+        <v>28.5</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2244,82 +2244,82 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>102.5676</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3666</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3173</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2405,24 +2405,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -2435,17 +2435,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,26 +2468,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>35.1</v>
+        <v>28.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>38</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>56.2</v>
+        <v>82</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2500,24 +2500,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2547,27 +2547,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2577,97 +2577,97 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2723,12 +2723,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,26 +2786,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.8</v>
+        <v>35.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
         <v>38</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>56.2</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2818,24 +2818,24 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -2865,27 +2865,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2895,67 +2895,67 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,11 +3104,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.2</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
@@ -3117,13 +3117,13 @@
         <v>38</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>77.40000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3183,27 +3183,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3213,67 +3213,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -3359,24 +3359,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3389,17 +3389,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,26 +3422,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R10" t="n">
         <v>38</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3454,24 +3454,24 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3531,97 +3531,97 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3677,24 +3677,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.3</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,14 +3740,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R11" t="n">
         <v>38</v>
@@ -3756,10 +3756,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>10.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3772,24 +3772,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3819,27 +3819,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3849,97 +3849,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3995,24 +3995,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4025,17 +4025,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4058,26 +4058,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>18.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>38</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>10.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4090,24 +4090,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4167,97 +4167,97 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -4313,24 +4313,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4343,17 +4343,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4380,22 +4380,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R13" t="n">
         <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T13" t="n">
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4408,24 +4408,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4455,27 +4455,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4485,97 +4485,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
         <v>9.6</v>
@@ -4707,13 +4707,13 @@
         <v>38</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4773,22 +4773,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -4803,67 +4803,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4949,24 +4949,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4979,17 +4979,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5016,22 +5016,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>38</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5044,24 +5044,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5121,97 +5121,97 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5330,11 +5330,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -5343,13 +5343,13 @@
         <v>38</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -5414,22 +5414,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/13, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5439,67 +5439,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>88.32</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.1996</t>
+          <t>99.2967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3243</t>
+          <t>0.3165</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.0721</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2642</t>
+          <t>0.2696</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.0449</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>38</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7040,12 +7040,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>52.7</v>
       </c>
       <c r="Q3" t="n">
         <v>21.5</v>
@@ -7339,13 +7339,13 @@
         <v>38</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>41.2</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -7358,12 +7358,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7410,17 +7410,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -7430,72 +7430,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>91.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0711</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4717</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.1998</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>45.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.2472</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -7581,24 +7581,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -7611,17 +7611,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7648,22 +7648,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R4" t="n">
         <v>38</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>34.9</v>
+        <v>41.2</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -7676,24 +7676,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -7738,112 +7738,112 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.2069</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7899,24 +7899,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -7929,17 +7929,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.4</v>
+        <v>47.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7962,26 +7962,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>38</v>
       </c>
       <c r="S5" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>66</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -7994,24 +7994,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -8046,22 +8046,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -8071,97 +8071,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.63</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.0711</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4717</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1998</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2472</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>502054</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Tommy Pham</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.1</v>
+        <v>44.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8280,11 +8280,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -8293,13 +8293,13 @@
         <v>38</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>44.1</v>
+        <v>28.5</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8312,12 +8312,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8359,12 +8359,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8374,82 +8374,82 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>102.5676</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3666</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3173</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8535,24 +8535,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8565,17 +8565,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8598,26 +8598,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>35.1</v>
+        <v>28.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>38</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>56.2</v>
+        <v>82</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8630,24 +8630,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8677,27 +8677,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8707,97 +8707,97 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8916,26 +8916,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.8</v>
+        <v>35.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
         <v>38</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>56.2</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8948,24 +8948,24 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -8995,27 +8995,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9025,67 +9025,67 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9234,11 +9234,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.2</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
@@ -9247,13 +9247,13 @@
         <v>38</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>77.40000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9266,12 +9266,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9313,27 +9313,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9343,67 +9343,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -9489,24 +9489,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9519,17 +9519,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9552,26 +9552,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R10" t="n">
         <v>38</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9584,24 +9584,24 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9631,12 +9631,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9661,97 +9661,97 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -9807,24 +9807,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.3</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9870,14 +9870,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R11" t="n">
         <v>38</v>
@@ -9886,10 +9886,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>10.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9902,24 +9902,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -9949,27 +9949,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9979,97 +9979,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -10125,24 +10125,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -10155,17 +10155,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10188,26 +10188,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>18.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>38</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>10.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10220,24 +10220,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10267,12 +10267,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10297,97 +10297,97 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -10443,24 +10443,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -10473,17 +10473,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10510,22 +10510,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R13" t="n">
         <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T13" t="n">
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10538,24 +10538,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10585,27 +10585,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10615,97 +10615,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -10761,12 +10761,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
         <v>9.6</v>
@@ -10837,13 +10837,13 @@
         <v>38</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10856,12 +10856,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10903,22 +10903,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -10933,67 +10933,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -11079,24 +11079,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -11109,17 +11109,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11146,22 +11146,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>38</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11174,24 +11174,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11251,97 +11251,97 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11460,11 +11460,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -11473,13 +11473,13 @@
         <v>38</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11492,12 +11492,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -11544,22 +11544,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/13, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11569,67 +11569,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>88.32</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.1996</t>
+          <t>99.2967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3243</t>
+          <t>0.3165</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.0721</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2642</t>
+          <t>0.2696</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.0449</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-08.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -888,10 +888,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,12 +1154,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1206,10 +1202,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1476,12 +1468,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,7 +1506,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1524,10 +1516,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -1541,39 +1533,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1794,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1818,7 +1806,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,7 +1820,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1842,10 +1830,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -1859,39 +1847,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2036,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2112,12 +2096,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,7 +2134,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2160,10 +2144,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -2177,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2354,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2430,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2454,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>41.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,7 +2448,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2478,10 +2458,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -2495,39 +2475,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2672,7 +2648,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2748,7 +2724,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,7 +2762,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2796,10 +2772,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2813,39 +2789,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -2990,7 +2962,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3041,12 +3013,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3066,12 +3038,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3090,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.8</v>
+        <v>38.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,26 +3076,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3131,39 +3103,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3183,27 +3151,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3213,67 +3181,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -3308,7 +3276,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3359,24 +3327,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3384,22 +3352,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3408,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,26 +3390,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3449,42 +3417,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3501,27 +3465,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3531,102 +3495,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3677,24 +3641,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3702,22 +3666,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3726,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.4</v>
+        <v>37.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,26 +3704,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3767,42 +3731,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3819,27 +3779,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3849,102 +3809,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3995,24 +3955,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4020,22 +3980,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4044,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4058,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4085,42 +4045,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4137,12 +4093,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4152,12 +4108,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4167,102 +4123,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4313,12 +4269,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4338,12 +4294,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4362,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>36.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4376,26 +4332,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4403,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4455,27 +4407,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4485,67 +4437,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4580,7 +4532,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4636,7 +4588,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4656,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4694,7 +4646,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4704,10 +4656,10 @@
         <v>9.6</v>
       </c>
       <c r="R14" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4721,39 +4673,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4898,7 +4846,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4974,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4998,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>34</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5012,7 +4960,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5022,10 +4970,10 @@
         <v>20.1</v>
       </c>
       <c r="R15" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -5039,39 +4987,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5216,7 +5160,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5267,24 +5211,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -5292,22 +5236,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5316,7 +5260,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.1</v>
+        <v>28.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5330,26 +5274,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>43.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5357,42 +5301,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5409,27 +5349,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5439,102 +5379,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5585,12 +5525,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5610,12 +5550,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5634,7 +5574,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5648,26 +5588,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5675,42 +5615,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5727,7 +5663,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5737,17 +5673,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5757,84 +5693,84 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>98.2866</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>0.299</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>97.253</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0.3524</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>0.1067</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>0.2943</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>69.86</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
       <c r="BF17" t="inlineStr">
         <is>
           <t>0.224</t>
@@ -5852,7 +5788,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5903,12 +5839,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5928,12 +5864,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5952,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.5</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5966,26 +5902,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R18" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S18" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5993,39 +5929,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6045,27 +5977,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6075,67 +6007,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6170,7 +6102,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6221,12 +6153,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6246,12 +6178,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6270,7 +6202,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.5</v>
+        <v>27.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6284,26 +6216,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>20.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S19" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>12</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6311,42 +6243,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -6363,27 +6291,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6393,67 +6321,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6488,7 +6416,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6970,7 +6898,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6994,7 +6922,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7008,7 +6936,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7018,10 +6946,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7035,39 +6963,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7212,7 +7136,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7288,12 +7212,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7312,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7326,7 +7250,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7336,10 +7260,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -7353,39 +7277,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7530,7 +7450,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7606,12 +7526,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7630,7 +7550,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7644,7 +7564,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7654,10 +7574,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -7671,39 +7591,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7848,7 +7764,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7924,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7948,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7962,7 +7878,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7972,10 +7888,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -7989,39 +7905,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8166,7 +8078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8242,12 +8154,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8266,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8280,7 +8192,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -8290,10 +8202,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -8307,39 +8219,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8484,7 +8392,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8560,7 +8468,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8584,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>41.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8598,7 +8506,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8608,10 +8516,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -8625,39 +8533,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8802,7 +8706,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8878,7 +8782,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8902,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8916,7 +8820,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8926,10 +8830,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -8943,39 +8847,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -9120,7 +9020,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9171,12 +9071,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9196,12 +9096,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9220,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.8</v>
+        <v>38.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9234,26 +9134,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9261,39 +9161,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9313,27 +9209,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9343,67 +9239,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -9438,7 +9334,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9489,24 +9385,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9514,22 +9410,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9538,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9552,26 +9448,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9579,42 +9475,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9631,27 +9523,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9661,102 +9553,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9807,24 +9699,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9832,22 +9724,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9856,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.4</v>
+        <v>37.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9870,26 +9762,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9897,42 +9789,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -9949,27 +9837,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9979,102 +9867,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10125,24 +10013,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -10150,22 +10038,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10174,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10188,26 +10076,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10215,42 +10103,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10267,12 +10151,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -10282,12 +10166,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10297,102 +10181,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10443,12 +10327,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10468,12 +10352,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10492,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>36.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10506,26 +10390,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10533,39 +10417,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10585,27 +10465,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10615,67 +10495,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10710,7 +10590,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10766,7 +10646,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10786,7 +10666,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10810,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10824,7 +10704,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10834,10 +10714,10 @@
         <v>9.6</v>
       </c>
       <c r="R14" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10851,39 +10731,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11028,7 +10904,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11104,7 +10980,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11128,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>34</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11142,7 +11018,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11152,10 +11028,10 @@
         <v>20.1</v>
       </c>
       <c r="R15" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -11169,39 +11045,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11346,7 +11218,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11397,24 +11269,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -11422,22 +11294,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11446,7 +11318,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.1</v>
+        <v>28.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11460,26 +11332,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>43.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11487,42 +11359,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11539,27 +11407,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11569,102 +11437,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11715,12 +11583,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11740,12 +11608,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11764,7 +11632,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11778,26 +11646,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11805,42 +11673,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11857,7 +11721,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -11867,17 +11731,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11887,84 +11751,84 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>98.2866</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>0.299</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>97.253</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0.3524</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>0.1067</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>0.2943</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>69.86</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
       <c r="BF17" t="inlineStr">
         <is>
           <t>0.224</t>
@@ -11982,7 +11846,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12033,12 +11897,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12058,12 +11922,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12082,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.5</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12096,26 +11960,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R18" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S18" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12123,39 +11987,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12175,27 +12035,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12205,67 +12065,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12300,7 +12160,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12351,12 +12211,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12376,12 +12236,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12400,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.5</v>
+        <v>27.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12414,26 +12274,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>20.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S19" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>12</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12441,42 +12301,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -12493,27 +12349,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12523,67 +12379,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12618,7 +12474,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
